--- a/Farol_Intensidade_CLEAR_2026.xlsx
+++ b/Farol_Intensidade_CLEAR_2026.xlsx
@@ -226,7 +226,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -236,6 +235,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,27 +650,27 @@
   <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="15" min="1" max="1"/>
-    <col width="28" customWidth="1" style="15" min="2" max="2"/>
-    <col width="7" customWidth="1" style="15" min="3" max="14"/>
+    <col width="16" customWidth="1" style="18" min="1" max="1"/>
+    <col width="28" customWidth="1" style="18" min="2" max="2"/>
+    <col width="7" customWidth="1" style="18" min="3" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.9" customHeight="1" s="15">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="25.9" customHeight="1" s="18">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Farol de Intensidade da Equipe — FGV CLEAR 2026</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.15" customHeight="1" s="15">
-      <c r="A2" s="18" t="inlineStr">
+    <row r="2" ht="22.15" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Cada pessoa preenche a sua linha com a percepção de carga em cada mês. Escala: 1 = tranquilo · 2 = ok · 3 = sobrecarga. A cor muda automaticamente.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="15">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="18">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Legenda:</t>
         </is>
@@ -696,7 +696,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22.15" customHeight="1" s="15">
+    <row r="4" ht="22.15" customHeight="1" s="18">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Pessoa</t>
@@ -768,7 +768,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22.15" customHeight="1" s="15">
+    <row r="5" ht="22.15" customHeight="1" s="18">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Bia B</t>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="22.15" customHeight="1" s="15">
+    <row r="6" ht="22.15" customHeight="1" s="18">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Bia S</t>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="22.15" customHeight="1" s="15">
+    <row r="7" ht="22.15" customHeight="1" s="18">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Caio</t>
@@ -912,7 +912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="22.15" customHeight="1" s="15">
+    <row r="8" ht="22.15" customHeight="1" s="18">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Carol</t>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="22.15" customHeight="1" s="15">
+    <row r="9" ht="22.15" customHeight="1" s="18">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Cecilia</t>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="22.15" customHeight="1" s="15">
+    <row r="10" ht="22.15" customHeight="1" s="18">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Fabrícia</t>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="22.15" customHeight="1" s="15">
+    <row r="11" ht="22.15" customHeight="1" s="18">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Fred</t>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="22.15" customHeight="1" s="15">
+    <row r="12" ht="22.15" customHeight="1" s="18">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Hisrael</t>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="22.15" customHeight="1" s="15">
+    <row r="13" ht="22.15" customHeight="1" s="18">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Julia</t>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="22.15" customHeight="1" s="15">
+    <row r="14" ht="22.15" customHeight="1" s="18">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Junior</t>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="22.15" customHeight="1" s="15">
+    <row r="15" ht="22.15" customHeight="1" s="18">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Lorena</t>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="22.15" customHeight="1" s="15">
+    <row r="16" ht="22.15" customHeight="1" s="18">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Luan</t>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="22.15" customHeight="1" s="15">
+    <row r="17" ht="22.15" customHeight="1" s="18">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Luigi</t>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="22.15" customHeight="1" s="15">
+    <row r="18" ht="22.15" customHeight="1" s="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Lycia</t>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="22.15" customHeight="1" s="15">
+    <row r="19" ht="22.15" customHeight="1" s="18">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Michel</t>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="22.15" customHeight="1" s="15">
+    <row r="20" ht="22.15" customHeight="1" s="18">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Samu</t>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="22.15" customHeight="1" s="15">
+    <row r="21" ht="22.15" customHeight="1" s="18">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TOTAL EQUIPE</t>
@@ -1547,57 +1547,44 @@
           <t>Soma de alocações por mês</t>
         </is>
       </c>
-      <c r="C21" s="5">
-        <f>SUM(C5:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="5">
-        <f>SUM(D5:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="5">
-        <f>SUM(E5:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="5">
-        <f>SUM(F5:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="5">
-        <f>SUM(G5:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="5">
-        <f>SUM(H5:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="5">
-        <f>SUM(I5:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="5">
-        <f>SUM(J5:J20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="5">
-        <f>SUM(K5:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="5">
-        <f>SUM(L5:L20)</f>
-        <v/>
-      </c>
-      <c r="M21" s="5">
-        <f>SUM(M5:M20)</f>
-        <v/>
-      </c>
-      <c r="N21" s="5">
-        <f>SUM(N5:N20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23" ht="31.9" customHeight="1" s="15">
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="31.9" customHeight="1" s="18">
       <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Instrução: cada pessoa preenche a sua linha com a percepção de carga em cada mês, usando a escala 1 a 3. 1 = tranquilo (carga leve). 2 = ok (carga normal). 3 = sobrecarga (sentindo apertado). A cor muda automaticamente. Não edite a linha de outras pessoas.</t>
